--- a/OUTPUT/reverse_A0A072Z841_Corynebacterium_glutamicum_ATCC_13032.xlsx
+++ b/OUTPUT/reverse_A0A072Z841_Corynebacterium_glutamicum_ATCC_13032.xlsx
@@ -477,16 +477,16 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>GAA</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>TTC</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>AAG</t>
-        </is>
-      </c>
       <c r="G2" t="n">
-        <v>0.0332</v>
+        <v>0.03338664534186325</v>
       </c>
     </row>
     <row r="3">
@@ -506,16 +506,16 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>TC</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>CT</t>
-        </is>
-      </c>
       <c r="G3" t="n">
-        <v>0.8104</v>
+        <v>0.8102758896441423</v>
       </c>
     </row>
   </sheetData>
